--- a/application_audit.xlsx
+++ b/application_audit.xlsx
@@ -7,7 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="results" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="priority_view" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="raw_details" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dashboard" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -122,6 +124,366 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Status Distribution</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <pieChart>
+        <varyColors val="1"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'dashboard'!E1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'dashboard'!$D$2</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'dashboard'!$E$2</f>
+            </numRef>
+          </val>
+        </ser>
+        <firstSliceAng val="0"/>
+      </pieChart>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Average Match by Platform</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'dashboard'!H1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'dashboard'!$G$2</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'dashboard'!$H$2</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Platform</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Score</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="13"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Posting Freshness</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'dashboard'!L1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'dashboard'!$K$2:$K$6</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'dashboard'!$L$2:$L$6</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Days Since Posted</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Count</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>11</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3240000" cy="2520000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>11</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3240000" cy="2520000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="2" name="Chart 2"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>11</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3240000" cy="2520000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="3" name="Chart 3"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -413,268 +775,2330 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC2"/>
+  <dimension ref="A1:T9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>job_id</t>
+          <t>pick_id</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>apply_decision</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>priority_level</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>match_score</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>target_tier</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>suggested_positioning</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>posted_priority</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>job_posted_date</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>days_since_posted</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>role_lock</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
           <t>platform</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>company</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>resume_file</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>resume_safe_file</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>resume_aggressive_file</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>resume_human_file</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>cover_letter_file</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>template_used</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>role_lock</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>keywords_injected</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>match_score</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>ats_match_score_llm</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>ats_score</t>
-        </is>
-      </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>section_score</t>
+          <t>matched_tier1_keywords</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>ats_keywords_used</t>
+          <t>suggested_improvements</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>covered_keywords</t>
+          <t>application_url</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>missing_keywords</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>missing_keywords_llm</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>risk_flags</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>improvements</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>remove_for_clarity</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>strict_profile_facts_used</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
           <t>job_url</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>timestamp</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>auto_step</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>applied_at</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>seek_quick_001</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>ReadyToApply</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Apply</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>84.2</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Fresh</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>The Banyans Medical Center</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Business Systems Analyst (AI &amp; Operations)</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Business Systems Analyst (AI &amp; Operations)</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
           <t>seek</t>
         </is>
       </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>C:\Users\Administrator\Desktop\AI job\outputs\applications\The_Banyans_Medical_Center_seek_scrape_002_resume.docx</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>C:\Users\Administrator\Desktop\AI job\outputs\applications\The_Banyans_Medical_Center_seek_scrape_002_coverletter.docx</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>https://www.seek.com.au/job/91520601</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>https://www.seek.com.au/job/91520601</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>1002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ReadyToApply</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Apply</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Fresh</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>National Pumping &amp; Irrigation</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Group Accounts Payable Officer</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Group Accounts Payable Officer</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>seek</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>C:\Users\Administrator\Desktop\AI job\outputs\applications\National_Pumping_Irrigation_resume.docx</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>C:\Users\Administrator\Desktop\AI job\outputs\applications\National_Pumping_Irrigation_coverletter.docx</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>accounts payable</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Refine the summary so the target role, strongest verified achievements, and core tools appear naturally in full sentences. | Strengthen selected experience bullets by tying role-relevant skills to measurable business outcomes.</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>https://www.seek.com.au/job/91447648</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>https://www.seek.com.au/job/91447648</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ReadyToApply</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Apply</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>71.8</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Aging</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Australian Country Choice</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Business Analyst – Manufacturing</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Business Analyst – Manufacturing</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>seek</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>C:\Users\Administrator\Desktop\AI job\outputs\applications\Australian_Country_Choice_seek_scrape_005_resume.docx</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>C:\Users\Administrator\Desktop\AI job\outputs\applications\Australian_Country_Choice_seek_scrape_005_coverletter.docx</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Refine the summary so the target role, strongest verified achievements, and core tools appear naturally in full sentences.</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>https://www.seek.com.au/job/91463394</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>https://www.seek.com.au/job/91463394</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ReadyToApply</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Apply</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Fresh</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Auto &amp; General</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Business Analyst (92499)</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Business Analyst (92499)</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>seek</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>C:\Users\Administrator\Desktop\AI job\outputs\applications\Auto_General_seek_scrape_004_resume.docx</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>C:\Users\Administrator\Desktop\AI job\outputs\applications\Auto_General_seek_scrape_004_coverletter.docx</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>process analysis</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>Refine the summary so the target role, strongest verified achievements, and core tools appear naturally in full sentences. | Tighten skills into fewer role-relevant categories and replace flat lists with capability-oriented wording. | Strengthen selected experience bullets by tying role-relevant skills to measurable business outcomes.</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>https://www.seek.com.au/job/91143043</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>https://www.seek.com.au/job/91143043</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>1005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ReadyToApply</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Apply</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>54.0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Old</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Ainslie Group</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Assistant Accountant</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Assistant Accountant</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>seek</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>C:\Users\Administrator\Desktop\AI job\outputs\applications\Ainslie_Group_resume.docx</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>C:\Users\Administrator\Desktop\AI job\outputs\applications\Ainslie_Group_coverletter.docx</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>Refine the summary so the target role, strongest verified achievements, and core tools appear naturally in full sentences. | Tighten skills into fewer role-relevant categories and replace flat lists with capability-oriented wording. | Strengthen selected experience bullets by tying role-relevant skills to measurable business outcomes.</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>https://www.seek.com.au/job/91304510</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>https://www.seek.com.au/job/91304510</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>1001</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ReadyToApply</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>44.7</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Aging</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Tanda</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Tanda Graduate Entry Roles (May - July 2026 Start)</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Tanda Graduate Entry Roles (May - July 2026 Start)</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>seek</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>C:\Users\Administrator\Desktop\AI job\outputs\applications\Tanda_seek_scrape_001_resume.docx</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>C:\Users\Administrator\Desktop\AI job\outputs\applications\Tanda_seek_scrape_001_coverletter.docx</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>Refine the summary so the target role, strongest verified achievements, and core tools appear naturally in full sentences. | Tighten skills into fewer role-relevant categories and replace flat lists with capability-oriented wording. | Strengthen selected experience bullets by tying role-relevant skills to measurable business outcomes.</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>https://www.seek.com.au/job/91462061</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>https://www.seek.com.au/job/91462061</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>1007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ReadyToApply</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Apply</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>43.2</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Abound Business Solutions</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Graduate Accountant</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Graduate Accountant</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>seek</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>C:\Users\Administrator\Desktop\AI job\outputs\applications\Abound_Business_Solutions_resume.docx</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>C:\Users\Administrator\Desktop\AI job\outputs\applications\Abound_Business_Solutions_coverletter.docx</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>Refine the summary so the target role, strongest verified achievements, and core tools appear naturally in full sentences. | Tighten skills into fewer role-relevant categories and replace flat lists with capability-oriented wording. | Strengthen selected experience bullets by tying role-relevant skills to measurable business outcomes.</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>https://www.seek.com.au/job/91606089</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>https://www.seek.com.au/job/91606089</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ReadyToApply</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Apply</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>34.8</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Newington Management</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Graduate - Project Manager (Client Side)</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Graduate - Project Manager (Client Side)</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>seek</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>C:\Users\Administrator\Desktop\AI job\outputs\applications\Newington_Management_resume.docx</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>C:\Users\Administrator\Desktop\AI job\outputs\applications\Newington_Management_coverletter.docx</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>Refine the summary so the target role, strongest verified achievements, and core tools appear naturally in full sentences. | Tighten skills into fewer role-relevant categories and replace flat lists with capability-oriented wording. | Strengthen selected experience bullets by tying role-relevant skills to measurable business outcomes.</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>https://www.seek.com.au/job/91605962</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>https://www.seek.com.au/job/91605962</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AK9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>pick_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>apply_decision</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>priority_level</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>match_score</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>target_tier</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>suggested_positioning</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>posted_priority</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>job_posted_date</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>days_since_posted</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>role_lock</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>resume_file</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>cover_letter_file</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>matched_tier1_keywords</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>suggested_improvements</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>application_url</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>job_url</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>job_id</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>template_used</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>ats_score</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>skill_match_score</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>experience_alignment_score</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>career_value_score</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>interview_probability_score</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>cv_focus</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>cover_letter_tone</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>decision_notes</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>interview_talking_points</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>recruiter_outreach_message</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>section_score</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>improvements</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>timestamp</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>resume_human_file</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>strict_profile_facts_used</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ReadyToApply</t>
+        </is>
+      </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>AQCare</t>
+          <t>Apply</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Administration Officer</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>ready_for_review</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>C:\Users\Administrator\Documents\New project\outputs\applications\AQCare_resume.docx</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
+          <t>Tier 1</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Fresh</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>C:\Users\Administrator\Documents\New project\outputs\applications\AQCare_resume.docx</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>C:\Users\Administrator\Documents\New project\outputs\applications\AQCare_coverletter.docx</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Douglas_Mo_Resume_Formatted.docx</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+          <t>The Banyans Medical Center</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Business Systems Analyst (AI &amp; Operations)</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Business Systems Analyst (AI &amp; Operations)</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>64.1</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr"/>
+          <t>seek</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>C:\Users\Administrator\Desktop\AI job\outputs\applications\The_Banyans_Medical_Center_seek_scrape_002_resume.docx</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>64.1</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>management, data, disability, scheduling, teams, accurate, admin, administration., administrative, advantageous., aged, analysis, collaboration, communication</t>
-        </is>
-      </c>
+          <t>C:\Users\Administrator\Desktop\AI job\outputs\applications\The_Banyans_Medical_Center_seek_scrape_002_coverletter.docx</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
-          <t>management, data, disability, scheduling, teams, accurate, admin, administration., administrative, advantageous., aged, analysis, collaboration, communication</t>
+          <t>https://www.seek.com.au/job/91520601</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>autonomously, bookings, cancellations, care, client, clients., community, confidential, contact, creative</t>
+          <t>https://www.seek.com.au/job/91520601</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Douglas Mo | Business Analyst | Data &amp; AI Analytics | Finance &amp; Commercial Operations | Brisbane, Australia | d157156@gmail.com | 0434 001 262 | International Student Visa (24h/week during semester, full-time during breaks). Target 485 Graduate Visa after graduation. | Available to start immediately for part-time or internship roles. Full-time from July 2026. | Identified $1.8M at-risk revenue through dashboarding and analysis</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>https://www.seek.com.au/job/91119474?origin=cardTitle&amp;ref=search-standalone&amp;type=standard</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>2026-04-11T23:49:06</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>clicked_apply_step; autofill fields=0 upload=0 cover=0; submit_not_found</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>2026-04-11T23:49:21</t>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>1002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ReadyToApply</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Apply</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Fresh</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>National Pumping &amp; Irrigation</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Group Accounts Payable Officer</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Group Accounts Payable Officer</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>seek</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>C:\Users\Administrator\Desktop\AI job\outputs\applications\National_Pumping_Irrigation_resume.docx</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>C:\Users\Administrator\Desktop\AI job\outputs\applications\National_Pumping_Irrigation_coverletter.docx</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>accounts payable</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Refine the summary so the target role, strongest verified achievements, and core tools appear naturally in full sentences. | Strengthen selected experience bullets by tying role-relevant skills to measurable business outcomes.</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>https://www.seek.com.au/job/91447648</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>https://www.seek.com.au/job/91447648</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ReadyToApply</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Apply</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>71.8</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Aging</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Australian Country Choice</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Business Analyst – Manufacturing</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Business Analyst – Manufacturing</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>seek</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>C:\Users\Administrator\Desktop\AI job\outputs\applications\Australian_Country_Choice_seek_scrape_005_resume.docx</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>C:\Users\Administrator\Desktop\AI job\outputs\applications\Australian_Country_Choice_seek_scrape_005_coverletter.docx</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Refine the summary so the target role, strongest verified achievements, and core tools appear naturally in full sentences.</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>https://www.seek.com.au/job/91463394</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>https://www.seek.com.au/job/91463394</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ReadyToApply</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Apply</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Fresh</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Auto &amp; General</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Business Analyst (92499)</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Business Analyst (92499)</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>seek</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>C:\Users\Administrator\Desktop\AI job\outputs\applications\Auto_General_seek_scrape_004_resume.docx</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>C:\Users\Administrator\Desktop\AI job\outputs\applications\Auto_General_seek_scrape_004_coverletter.docx</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>process analysis</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>Refine the summary so the target role, strongest verified achievements, and core tools appear naturally in full sentences. | Tighten skills into fewer role-relevant categories and replace flat lists with capability-oriented wording. | Strengthen selected experience bullets by tying role-relevant skills to measurable business outcomes.</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>https://www.seek.com.au/job/91143043</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>https://www.seek.com.au/job/91143043</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>1005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ReadyToApply</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Apply</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>54.0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Old</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Ainslie Group</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Assistant Accountant</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Assistant Accountant</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>seek</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>C:\Users\Administrator\Desktop\AI job\outputs\applications\Ainslie_Group_resume.docx</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>C:\Users\Administrator\Desktop\AI job\outputs\applications\Ainslie_Group_coverletter.docx</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>Refine the summary so the target role, strongest verified achievements, and core tools appear naturally in full sentences. | Tighten skills into fewer role-relevant categories and replace flat lists with capability-oriented wording. | Strengthen selected experience bullets by tying role-relevant skills to measurable business outcomes.</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>https://www.seek.com.au/job/91304510</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>https://www.seek.com.au/job/91304510</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>1001</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ReadyToApply</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>44.7</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Aging</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Tanda</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Tanda Graduate Entry Roles (May - July 2026 Start)</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Tanda Graduate Entry Roles (May - July 2026 Start)</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>seek</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>C:\Users\Administrator\Desktop\AI job\outputs\applications\Tanda_seek_scrape_001_resume.docx</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>C:\Users\Administrator\Desktop\AI job\outputs\applications\Tanda_seek_scrape_001_coverletter.docx</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>Refine the summary so the target role, strongest verified achievements, and core tools appear naturally in full sentences. | Tighten skills into fewer role-relevant categories and replace flat lists with capability-oriented wording. | Strengthen selected experience bullets by tying role-relevant skills to measurable business outcomes.</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>https://www.seek.com.au/job/91462061</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>https://www.seek.com.au/job/91462061</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>1007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ReadyToApply</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Apply</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>43.2</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Abound Business Solutions</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Graduate Accountant</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Graduate Accountant</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>seek</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>C:\Users\Administrator\Desktop\AI job\outputs\applications\Abound_Business_Solutions_resume.docx</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>C:\Users\Administrator\Desktop\AI job\outputs\applications\Abound_Business_Solutions_coverletter.docx</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>Refine the summary so the target role, strongest verified achievements, and core tools appear naturally in full sentences. | Tighten skills into fewer role-relevant categories and replace flat lists with capability-oriented wording. | Strengthen selected experience bullets by tying role-relevant skills to measurable business outcomes.</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>https://www.seek.com.au/job/91606089</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>https://www.seek.com.au/job/91606089</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>seek_manual_001</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Douglas_Mo_Resume_Formatted.docx</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>43.2</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>43.2</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>57.0</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>76.5</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>47.3</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>Target tier: Tier 2 | Suggested positioning: Finance | ATS score: 43.2</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>Position yourself as a realistic fit for Graduate Accountant by linking prior work to the role's day-to-day workflows. | Lead with this verified evidence: Experience with reconciliations across cash management, bank activity, and reporting workflows..</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>Hi, I have applied for the Graduate Accountant role at Abound Business Solutions. My background combines finance-relevant experience across finance, reporting, and process improvement, and I would welcome the chance to discuss how I could contribute quickly.</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Refine the summary so the target role, strongest verified achievements, and core tools appear naturally in full sentences. | Tighten skills into fewer role-relevant categories and replace flat lists with capability-oriented wording. | Strengthen selected experience bullets by tying role-relevant skills to measurable business outcomes.</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>2026-04-21T03:25:15</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>C:\Users\Administrator\Desktop\AI job\outputs\applications\Abound_Business_Solutions_resume.docx</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Experience with reconciliations across cash management, bank activity, and reporting workflows. | Experience with month-end support, reporting preparation, and close-process discipline. | Delivered financial reporting, performance tracking, and finance analysis across operational workflows. | Experience with profit and loss reporting, performance tracking, and finance decision support. | Delivered tax compliance work across high-volume filings with accuracy and reporting discipline. | Experience with accounts payable coordination, payment scheduling, and finance operations support. | Hands-on exposure to SAP and ERP-supported finance workflows. | Hands-on experience with QuickBooks for finance operations and reporting workflows.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ReadyToApply</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Apply</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>34.8</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Newington Management</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Graduate - Project Manager (Client Side)</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Graduate - Project Manager (Client Side)</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>seek</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>C:\Users\Administrator\Desktop\AI job\outputs\applications\Newington_Management_resume.docx</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>C:\Users\Administrator\Desktop\AI job\outputs\applications\Newington_Management_coverletter.docx</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>Refine the summary so the target role, strongest verified achievements, and core tools appear naturally in full sentences. | Tighten skills into fewer role-relevant categories and replace flat lists with capability-oriented wording. | Strengthen selected experience bullets by tying role-relevant skills to measurable business outcomes.</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>https://www.seek.com.au/job/91605962</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>https://www.seek.com.au/job/91605962</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>seek_manual_002</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Douglas_Mo_Resume_Formatted.docx</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>34.8</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>34.8</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>60.0</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>44.4</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>Target tier: Tier 3 | Suggested positioning: Hybrid | ATS score: 34.8</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>Position yourself as a realistic fit for Graduate - Project Manager (Client Side) by linking prior work to the role's day-to-day workflows. | Lead with this verified evidence: Business Analyst | Data &amp; AI Analytics | Finance &amp; Commercial Operations.</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>Hi, I have applied for the Graduate - Project Manager (Client Side) role at Newington Management. My background combines hybrid-relevant experience across finance, reporting, and process improvement, and I would welcome the chance to discuss how I could contribute quickly.</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Refine the summary so the target role, strongest verified achievements, and core tools appear naturally in full sentences. | Tighten skills into fewer role-relevant categories and replace flat lists with capability-oriented wording. | Strengthen selected experience bullets by tying role-relevant skills to measurable business outcomes.</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>2026-04-21T03:25:15</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>C:\Users\Administrator\Desktop\AI job\outputs\applications\Newington_Management_resume.docx</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Business Analyst | Data &amp; AI Analytics | Finance &amp; Commercial Operations | I'm Douglas Mo, bridging business operations and AI technology. With 2+ years international accounting experience (managing $12M annual revenue) and intensive AI development training, I build production-grade intelligent systems that solve real business proble | Zhongshan Hengrun Taxation Firm metrics: filings completed: 1000+, accuracy rate: 100% (zero penalties), efficiency improvement: 35% faster reporting cycle | Delivered tax compliance work across high-volume filings with accuracy and reporting discipline. | Work authorization: International Student Visa (max 24 hours/week until graduation June 2026, then 485 Graduate Visa with full-time work rights) | Experience with month-end support, reporting preparation, and close-process discipline. | Experience with profit and loss reporting, performance tracking, and finance decision support. | Experience with accounts payable coordination, payment scheduling, and finance operations support.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Platform</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Avg Match</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Posted Bucket</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Missing Keyword</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Total Roles</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>8</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>ReadyToApply</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>8</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>seek</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>59.3</v>
+      </c>
+      <c r="I2" t="n">
+        <v>8</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0-3 days</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Average Match Score</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>59.3</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>4-7 days</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>High Match (&gt;=70)</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>8-14 days</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>High Match Rate %</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>15+ days</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Posted-Date Coverage %</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>100</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Fresh Jobs (&lt;=7d) %</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>62.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Avg Days Since Posted</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>6.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
 </file>